--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,511 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128621019</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>545445</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7013092</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128621018</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545455</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7013445</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128621036</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545298</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7013509</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128621016</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92736</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>545443</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7013476</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128621020</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92736</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>545453</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7013336</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>128621019</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128621018</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128621036</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>128621019</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128621018</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128621036</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>128621019</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128621018</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128621036</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>128621019</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128621018</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128621036</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>128621019</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128621018</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128621036</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>128621019</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128621018</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128621036</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>128621019</v>
       </c>
       <c r="B4" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128621018</v>
       </c>
       <c r="B5" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128621036</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>128621019</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128621018</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128621036</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128621016</v>
       </c>
       <c r="B7" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>128621020</v>
       </c>
       <c r="B8" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7084485</v>
+        <v>104024863</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ammerån, V sidan, N om Stugutjärnen, Jmt</t>
+          <t>Stugutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545296.9506689452</v>
+        <v>545363</v>
       </c>
       <c r="R2" t="n">
-        <v>7013476.87630313</v>
+        <v>7013328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,45 +766,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre tallskog med diameterspridning</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>sandmark bland lav och lingon, väggmossa, ljung</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104024863</v>
+        <v>7084486</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stugutjärnen, Jmt</t>
+          <t>Ammerån, V sidan, N om Stugutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545362.6594050836</v>
+        <v>545318</v>
       </c>
       <c r="R3" t="n">
-        <v>7013328.647062323</v>
+        <v>7013404</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:06</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:06</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,65 +867,87 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre åstallskog med diameterspridning</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # hård tallåga efter lumpad topp</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128621019</v>
+        <v>7084488</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>92692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1958</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>stugutjärnen, ammerån, Jmt</t>
+          <t>Ammerån, V sidan, N om Stugutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545445</v>
+        <v>545292</v>
       </c>
       <c r="R4" t="n">
-        <v>7013092</v>
+        <v>7013574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,12 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,16 +990,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre åstallskog med stor diameterspridning</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>stig på åskrön</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1027,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128621018</v>
+        <v>7084489</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,34 +1031,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>stugutjärnen, ammerån, Jmt</t>
+          <t>Ammerån, V sidan, N om Stugutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545455</v>
+        <v>545294</v>
       </c>
       <c r="R5" t="n">
-        <v>7013445</v>
+        <v>7013568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,12 +1094,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,16 +1110,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre åstallskog med stor diameterspridning</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>stig på åskrön</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1128,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128621036</v>
+        <v>128621016</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545298</v>
+        <v>545443</v>
       </c>
       <c r="R6" t="n">
-        <v>7013509</v>
+        <v>7013476</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128621016</v>
+        <v>128621020</v>
       </c>
       <c r="B7" t="n">
-        <v>92813</v>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545443</v>
+        <v>545453</v>
       </c>
       <c r="R7" t="n">
-        <v>7013476</v>
+        <v>7013336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128621020</v>
+        <v>104024861</v>
       </c>
       <c r="B8" t="n">
-        <v>92813</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,34 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>stugutjärnen, ammerån, Jmt</t>
+          <t>Stugutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545453</v>
+        <v>545358</v>
       </c>
       <c r="R8" t="n">
-        <v>7013336</v>
+        <v>7013302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,12 +1407,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,15 +1437,429 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104024866</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stugutjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>545394</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7013058</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128621036</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>545298</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7013509</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128621018</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>545455</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7013445</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128621019</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>545445</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7013092</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 35344-2025 artfynd.xlsx
+++ b/artfynd/A 35344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024863</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084486</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084488</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084489</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128621016</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128621020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024861</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024866</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128621036</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1763,6 +1813,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128621018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,8 +1919,26 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128621019</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>